--- a/RegistrosPRE.xlsx
+++ b/RegistrosPRE.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/luli/Desktop/StroopTest/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/luli/Desktop/Cognitio/StroopTest/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{846535C8-6829-8B4D-9902-84C267CD9CE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C66A19DB-D3A8-C84D-9F56-878389E311B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="200" yWindow="0" windowWidth="28040" windowHeight="16320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/RegistrosPRE.xlsx
+++ b/RegistrosPRE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/luli/Desktop/Cognitio/StroopTest/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C66A19DB-D3A8-C84D-9F56-878389E311B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{392809B8-5F3B-F241-B289-6500A4C5394B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="200" yWindow="0" windowWidth="28040" windowHeight="16320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
     <t>PC</t>
   </si>
   <si>
-    <t>Pccorregido</t>
+    <t>PCcorregido</t>
   </si>
   <si>
     <t>TPC</t>
